--- a/src/main/kotlin/com/kcvn/spm/assets/template/Import_GiaTape_template.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/Import_GiaTape_template.xlsx
@@ -30,10 +30,10 @@
     <t>Đơn giá</t>
   </si>
   <si>
-    <t>Loại tape</t>
+    <t>Loại xuất hàng</t>
   </si>
   <si>
-    <t>Loại xuất hàng</t>
+    <t>Loại TAPE</t>
   </si>
 </sst>
 </file>
@@ -406,13 +406,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
